--- a/artfynd/A 21599-2024 artfynd.xlsx
+++ b/artfynd/A 21599-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131157</v>
+        <v>122131155</v>
       </c>
       <c r="B2" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>703003</v>
+        <v>702980</v>
       </c>
       <c r="R2" t="n">
-        <v>7204911</v>
+        <v>7204815</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131153</v>
+        <v>122131157</v>
       </c>
       <c r="B3" t="n">
-        <v>90797</v>
+        <v>78646</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>703070</v>
+        <v>703003</v>
       </c>
       <c r="R3" t="n">
-        <v>7204709</v>
+        <v>7204911</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131155</v>
+        <v>122131153</v>
       </c>
       <c r="B4" t="n">
-        <v>78645</v>
+        <v>90807</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>702980</v>
+        <v>703070</v>
       </c>
       <c r="R4" t="n">
-        <v>7204815</v>
+        <v>7204709</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 21599-2024 artfynd.xlsx
+++ b/artfynd/A 21599-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131155</v>
+        <v>122131153</v>
       </c>
       <c r="B2" t="n">
-        <v>78646</v>
+        <v>90807</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>702980</v>
+        <v>703070</v>
       </c>
       <c r="R2" t="n">
-        <v>7204815</v>
+        <v>7204709</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131153</v>
+        <v>122131155</v>
       </c>
       <c r="B4" t="n">
-        <v>90807</v>
+        <v>78646</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>703070</v>
+        <v>702980</v>
       </c>
       <c r="R4" t="n">
-        <v>7204709</v>
+        <v>7204815</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 21599-2024 artfynd.xlsx
+++ b/artfynd/A 21599-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131153</v>
+        <v>122131157</v>
       </c>
       <c r="B2" t="n">
-        <v>90807</v>
+        <v>78651</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>703070</v>
+        <v>703003</v>
       </c>
       <c r="R2" t="n">
-        <v>7204709</v>
+        <v>7204911</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131157</v>
+        <v>122131153</v>
       </c>
       <c r="B3" t="n">
-        <v>78646</v>
+        <v>90819</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>703003</v>
+        <v>703070</v>
       </c>
       <c r="R3" t="n">
-        <v>7204911</v>
+        <v>7204709</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,7 +890,7 @@
         <v>122131155</v>
       </c>
       <c r="B4" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 21599-2024 artfynd.xlsx
+++ b/artfynd/A 21599-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131157</v>
+        <v>122131155</v>
       </c>
       <c r="B2" t="n">
         <v>78651</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>703003</v>
+        <v>702980</v>
       </c>
       <c r="R2" t="n">
-        <v>7204911</v>
+        <v>7204815</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,7 +784,7 @@
         <v>122131153</v>
       </c>
       <c r="B3" t="n">
-        <v>90819</v>
+        <v>90826</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131155</v>
+        <v>122131157</v>
       </c>
       <c r="B4" t="n">
         <v>78651</v>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>702980</v>
+        <v>703003</v>
       </c>
       <c r="R4" t="n">
-        <v>7204815</v>
+        <v>7204911</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 21599-2024 artfynd.xlsx
+++ b/artfynd/A 21599-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131155</v>
+        <v>122131157</v>
       </c>
       <c r="B2" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -693,11 +693,6 @@
       <c r="E2" t="n">
         <v>6425</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>702980</v>
+        <v>703003</v>
       </c>
       <c r="R2" t="n">
-        <v>7204815</v>
+        <v>7204911</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131153</v>
+        <v>122131155</v>
       </c>
       <c r="B3" t="n">
-        <v>90826</v>
+        <v>78652</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +792,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>703070</v>
+        <v>702980</v>
       </c>
       <c r="R3" t="n">
-        <v>7204709</v>
+        <v>7204815</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131157</v>
+        <v>122131153</v>
       </c>
       <c r="B4" t="n">
-        <v>78651</v>
+        <v>90831</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +893,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>5432</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>703003</v>
+        <v>703070</v>
       </c>
       <c r="R4" t="n">
-        <v>7204911</v>
+        <v>7204709</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 21599-2024 artfynd.xlsx
+++ b/artfynd/A 21599-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131157</v>
+        <v>122131155</v>
       </c>
       <c r="B2" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -693,6 +693,11 @@
       <c r="E2" t="n">
         <v>6425</v>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -710,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>703003</v>
+        <v>702980</v>
       </c>
       <c r="R2" t="n">
-        <v>7204911</v>
+        <v>7204815</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131155</v>
+        <v>122131157</v>
       </c>
       <c r="B3" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,6 +799,11 @@
       <c r="E3" t="n">
         <v>6425</v>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -811,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>702980</v>
+        <v>703003</v>
       </c>
       <c r="R3" t="n">
-        <v>7204815</v>
+        <v>7204911</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,7 +890,7 @@
         <v>122131153</v>
       </c>
       <c r="B4" t="n">
-        <v>90831</v>
+        <v>90844</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -894,6 +904,11 @@
       </c>
       <c r="E4" t="n">
         <v>5432</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>

--- a/artfynd/A 21599-2024 artfynd.xlsx
+++ b/artfynd/A 21599-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131155</v>
+        <v>122131157</v>
       </c>
       <c r="B2" t="n">
         <v>78656</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>702980</v>
+        <v>703003</v>
       </c>
       <c r="R2" t="n">
-        <v>7204815</v>
+        <v>7204911</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131157</v>
+        <v>122131153</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
+        <v>90857</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>703003</v>
+        <v>703070</v>
       </c>
       <c r="R3" t="n">
-        <v>7204911</v>
+        <v>7204709</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131153</v>
+        <v>122131155</v>
       </c>
       <c r="B4" t="n">
-        <v>90844</v>
+        <v>78656</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>703070</v>
+        <v>702980</v>
       </c>
       <c r="R4" t="n">
-        <v>7204709</v>
+        <v>7204815</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
